--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAÍSO INTERIOR CB.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_JAEN PARAÍSO INTERIOR CB.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. FELIZOR</t>
+          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
-        <v>8.328099999999999</v>
+        <v>5.622999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>9.749600000000001</v>
+        <v>4.9847</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.421399999999999</v>
+        <v>0.6384000000000005</v>
       </c>
       <c r="G2" t="n">
-        <v>-12.4241</v>
+        <v>-2.6681</v>
       </c>
       <c r="H2" t="n">
-        <v>-15.8598</v>
+        <v>-5.4231</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4353</v>
+        <v>2.755500000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>16.6904</v>
+        <v>7.548</v>
       </c>
       <c r="K2" t="n">
-        <v>4.2296</v>
+        <v>-0.06909999999999972</v>
       </c>
       <c r="L2" t="n">
-        <v>12.4607</v>
+        <v>7.616899999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-29.1145</v>
+        <v>-10.2159</v>
       </c>
       <c r="N2" t="n">
-        <v>-20.0892</v>
+        <v>-5.354200000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.025500000000001</v>
+        <v>-4.8616</v>
       </c>
       <c r="P2" t="n">
-        <v>-2.2894</v>
+        <v>8.949</v>
       </c>
       <c r="Q2" t="n">
-        <v>-40.9995</v>
+        <v>-10.8222</v>
       </c>
       <c r="R2" t="n">
-        <v>38.7099</v>
+        <v>19.7712</v>
       </c>
       <c r="S2" t="n">
-        <v>18.5554</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>11.0261</v>
+        <v>1.7312</v>
       </c>
       <c r="U2" t="n">
-        <v>7.5289</v>
+        <v>-2.3508</v>
       </c>
       <c r="V2" t="n">
-        <v>4.4861</v>
+        <v>-0.03889999999999982</v>
       </c>
       <c r="W2" t="n">
-        <v>23.0321</v>
+        <v>6.5276</v>
       </c>
       <c r="X2" t="n">
-        <v>-18.5458</v>
+        <v>-6.5665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. TIKHONENKO ANDRIYASHCHENKO</t>
+          <t>G. BOAHEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7794999999999992</v>
+        <v>3.581799999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0479</v>
+        <v>22.3497</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.2684</v>
+        <v>-18.7676</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.6681</v>
+        <v>5.6071</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.4231</v>
+        <v>-2.3871</v>
       </c>
       <c r="I3" t="n">
-        <v>2.755500000000001</v>
+        <v>7.994300000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>7.548</v>
+        <v>40.4247</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.06909999999999972</v>
+        <v>15.4129</v>
       </c>
       <c r="L3" t="n">
-        <v>7.616899999999999</v>
+        <v>25.0122</v>
       </c>
       <c r="M3" t="n">
-        <v>-10.2159</v>
+        <v>-34.8179</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.354200000000001</v>
+        <v>-17.7998</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.8616</v>
+        <v>-17.0179</v>
       </c>
       <c r="P3" t="n">
-        <v>8.949</v>
+        <v>-4.1624</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10.8222</v>
+        <v>-51.8217</v>
       </c>
       <c r="R3" t="n">
-        <v>19.7712</v>
+        <v>47.6591</v>
       </c>
       <c r="S3" t="n">
-        <v>-5.4626</v>
+        <v>-1.7616</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7945999999999999</v>
+        <v>0.7546000000000002</v>
       </c>
       <c r="U3" t="n">
-        <v>-6.257400000000001</v>
+        <v>-2.5161</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.03889999999999982</v>
+        <v>3.8988</v>
       </c>
       <c r="W3" t="n">
-        <v>6.5276</v>
+        <v>32.9916</v>
       </c>
       <c r="X3" t="n">
-        <v>-6.5665</v>
+        <v>-29.0926</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. BANQUERI MARIN</t>
+          <t>C. FIELDS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2081</v>
+        <v>1.273000000000002</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.835999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2081</v>
+        <v>-0.5627999999999993</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2857</v>
+        <v>-2.706399999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-8.4727</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2857</v>
+        <v>5.766199999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>15.2661</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>-1.019400000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>16.2856</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2857</v>
+        <v>-17.9727</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-7.4532</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2857</v>
+        <v>-10.5192</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2081</v>
+        <v>7.2841</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-17.482</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2081</v>
+        <v>24.7661</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2857</v>
+        <v>1.1743</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>0.1244999999999998</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2857</v>
+        <v>1.0499</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>-4.479100000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>3.9272</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-8.4062</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARTINEZ MEGIAS</t>
+          <t>G. BANQUERI MARIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-3.5978</v>
+        <v>0.2081</v>
       </c>
       <c r="E5" t="n">
-        <v>9.594799999999999</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.1927</v>
+        <v>0.2081</v>
       </c>
       <c r="G5" t="n">
-        <v>21.7184</v>
+        <v>0.2857</v>
       </c>
       <c r="H5" t="n">
-        <v>17.1937</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>4.525</v>
+        <v>0.2857</v>
       </c>
       <c r="J5" t="n">
-        <v>42.3132</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>29.9391</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>12.3749</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-20.5949</v>
+        <v>0.2857</v>
       </c>
       <c r="N5" t="n">
-        <v>-12.7454</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-7.849699999999999</v>
+        <v>0.2857</v>
       </c>
       <c r="P5" t="n">
-        <v>7.7003</v>
+        <v>0.2081</v>
       </c>
       <c r="Q5" t="n">
-        <v>-34.7559</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>42.4562</v>
+        <v>0.2081</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8393</v>
+        <v>-0.2857</v>
       </c>
       <c r="T5" t="n">
-        <v>9.466899999999999</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-4.6274</v>
+        <v>-0.2857</v>
       </c>
       <c r="V5" t="n">
-        <v>-37.8562</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>-7.4297</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-30.4264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MORENO POZA</t>
+          <t>K. FELIZOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>-4.0501</v>
+        <v>-1.0322</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9134000000000004</v>
+        <v>4.3919</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.1366</v>
+        <v>-5.4244</v>
       </c>
       <c r="G6" t="n">
-        <v>-7.4253</v>
+        <v>-12.4241</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.4533</v>
+        <v>-15.8598</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.9718</v>
+        <v>3.4353</v>
       </c>
       <c r="J6" t="n">
-        <v>5.7657</v>
+        <v>16.6904</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6104</v>
+        <v>4.2296</v>
       </c>
       <c r="L6" t="n">
-        <v>2.1556</v>
+        <v>12.4607</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.191</v>
+        <v>-29.1145</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.0637</v>
+        <v>-20.0892</v>
       </c>
       <c r="O6" t="n">
-        <v>-7.127199999999999</v>
+        <v>-9.025500000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>6.0353</v>
+        <v>-2.2894</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.2435</v>
+        <v>-40.9995</v>
       </c>
       <c r="R6" t="n">
-        <v>12.279</v>
+        <v>38.7099</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2277</v>
+        <v>9.194800000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6433999999999997</v>
+        <v>5.6689</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5844</v>
+        <v>3.526</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.8883</v>
+        <v>4.4861</v>
       </c>
       <c r="W6" t="n">
-        <v>-1.0791</v>
+        <v>23.0321</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.8092</v>
+        <v>-18.5458</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CAÑETE PUENTENUEVA</t>
+          <t>J. MORENO POZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>-4.178299999999998</v>
+        <v>-3.6983</v>
       </c>
       <c r="E7" t="n">
-        <v>2.3266</v>
+        <v>-1.1368</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.5046</v>
+        <v>-2.5612</v>
       </c>
       <c r="G7" t="n">
-        <v>-10.8662</v>
+        <v>-7.4253</v>
       </c>
       <c r="H7" t="n">
-        <v>-4.1252</v>
+        <v>-2.4533</v>
       </c>
       <c r="I7" t="n">
-        <v>-6.741099999999999</v>
+        <v>-4.9718</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2393999999999996</v>
+        <v>5.7657</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0293000000000001</v>
+        <v>3.6104</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2098999999999998</v>
+        <v>2.1556</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.6273</v>
+        <v>-13.191</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.095899999999999</v>
+        <v>-6.0637</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.5312</v>
+        <v>-7.127199999999999</v>
       </c>
       <c r="P7" t="n">
         <v>6.0353</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.3299</v>
+        <v>-6.2435</v>
       </c>
       <c r="R7" t="n">
-        <v>9.3652</v>
+        <v>12.279</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1682000000000006</v>
+        <v>1.5795</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4734</v>
+        <v>0.42</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.3052</v>
+        <v>1.1597</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4848000000000001</v>
+        <v>-3.8883</v>
       </c>
       <c r="W7" t="n">
-        <v>4.4226</v>
+        <v>-1.0791</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.9377</v>
+        <v>-2.8092</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. BOAHEN</t>
+          <t>A. CAÑETE PUENTENUEVA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.217900000000001</v>
+        <v>-5.0012</v>
       </c>
       <c r="E8" t="n">
-        <v>16.3253</v>
+        <v>1.0457</v>
       </c>
       <c r="F8" t="n">
-        <v>-21.5432</v>
+        <v>-6.0466</v>
       </c>
       <c r="G8" t="n">
-        <v>5.6071</v>
+        <v>-10.8662</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3871</v>
+        <v>-4.1252</v>
       </c>
       <c r="I8" t="n">
-        <v>7.994300000000001</v>
+        <v>-6.741099999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>40.4247</v>
+        <v>-0.2393999999999996</v>
       </c>
       <c r="K8" t="n">
-        <v>15.4129</v>
+        <v>-0.0293000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>25.0122</v>
+        <v>-0.2098999999999998</v>
       </c>
       <c r="M8" t="n">
-        <v>-34.8179</v>
+        <v>-10.6273</v>
       </c>
       <c r="N8" t="n">
-        <v>-17.7998</v>
+        <v>-4.095899999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-17.0179</v>
+        <v>-6.5312</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.1624</v>
+        <v>6.0353</v>
       </c>
       <c r="Q8" t="n">
-        <v>-51.8217</v>
+        <v>-3.3299</v>
       </c>
       <c r="R8" t="n">
-        <v>47.6591</v>
+        <v>9.3652</v>
       </c>
       <c r="S8" t="n">
-        <v>-10.5615</v>
+        <v>-0.6549999999999998</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.2697</v>
+        <v>0.1921999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-5.291700000000001</v>
+        <v>-0.8472999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>3.8988</v>
+        <v>0.4848000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>32.9916</v>
+        <v>4.4226</v>
       </c>
       <c r="X8" t="n">
-        <v>-29.0926</v>
+        <v>-3.9377</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. FIELDS</t>
+          <t>L. RODRIGUEZ DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.2175</v>
+        <v>-7.389100000000002</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.5524</v>
+        <v>-5.6485</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.665</v>
+        <v>-1.7405</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.706399999999999</v>
+        <v>-12.8574</v>
       </c>
       <c r="H9" t="n">
-        <v>-8.4727</v>
+        <v>-7.8134</v>
       </c>
       <c r="I9" t="n">
-        <v>5.766199999999999</v>
+        <v>-5.0439</v>
       </c>
       <c r="J9" t="n">
-        <v>15.2661</v>
+        <v>-2.1387</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.019400000000001</v>
+        <v>3.1014</v>
       </c>
       <c r="L9" t="n">
-        <v>16.2856</v>
+        <v>-5.2402</v>
       </c>
       <c r="M9" t="n">
-        <v>-17.9727</v>
+        <v>-10.7186</v>
       </c>
       <c r="N9" t="n">
-        <v>-7.4532</v>
+        <v>-10.9146</v>
       </c>
       <c r="O9" t="n">
-        <v>-10.5192</v>
+        <v>0.196</v>
       </c>
       <c r="P9" t="n">
-        <v>7.2841</v>
+        <v>14.5682</v>
       </c>
       <c r="Q9" t="n">
-        <v>-17.482</v>
+        <v>-5.619199999999999</v>
       </c>
       <c r="R9" t="n">
-        <v>24.7661</v>
+        <v>20.1874</v>
       </c>
       <c r="S9" t="n">
-        <v>-11.3161</v>
+        <v>-6.648300000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-9.263500000000001</v>
+        <v>-1.8528</v>
       </c>
       <c r="U9" t="n">
-        <v>-2.0524</v>
+        <v>-4.7952</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.479100000000001</v>
+        <v>-2.4519</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9272</v>
+        <v>3.9626</v>
       </c>
       <c r="X9" t="n">
-        <v>-8.4062</v>
+        <v>-6.414300000000001</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ DOMINGUEZ</t>
+          <t>J. MARTINEZ MEGIAS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-13.6273</v>
+        <v>-10.0734</v>
       </c>
       <c r="E10" t="n">
-        <v>-9.557400000000001</v>
+        <v>3.049100000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.0699</v>
+        <v>-13.1224</v>
       </c>
       <c r="G10" t="n">
-        <v>-12.8574</v>
+        <v>21.7184</v>
       </c>
       <c r="H10" t="n">
-        <v>-7.8134</v>
+        <v>17.1937</v>
       </c>
       <c r="I10" t="n">
-        <v>-5.0439</v>
+        <v>4.525</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.1387</v>
+        <v>42.3132</v>
       </c>
       <c r="K10" t="n">
-        <v>3.1014</v>
+        <v>29.9391</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.2402</v>
+        <v>12.3749</v>
       </c>
       <c r="M10" t="n">
-        <v>-10.7186</v>
+        <v>-20.5949</v>
       </c>
       <c r="N10" t="n">
-        <v>-10.9146</v>
+        <v>-12.7454</v>
       </c>
       <c r="O10" t="n">
-        <v>0.196</v>
+        <v>-7.849699999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>14.5682</v>
+        <v>7.7003</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.619199999999999</v>
+        <v>-34.7559</v>
       </c>
       <c r="R10" t="n">
-        <v>20.1874</v>
+        <v>42.4562</v>
       </c>
       <c r="S10" t="n">
-        <v>-12.8863</v>
+        <v>-1.6359</v>
       </c>
       <c r="T10" t="n">
-        <v>-5.761900000000001</v>
+        <v>2.9213</v>
       </c>
       <c r="U10" t="n">
-        <v>-7.1242</v>
+        <v>-4.5574</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.4519</v>
+        <v>-37.8562</v>
       </c>
       <c r="W10" t="n">
-        <v>3.9626</v>
+        <v>-7.4297</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.414300000000001</v>
+        <v>-30.4264</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-15.3563</v>
+        <v>-13.576</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.1137</v>
+        <v>-12.7271</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2425</v>
+        <v>-0.8488999999999998</v>
       </c>
       <c r="G11" t="n">
         <v>-5.8973</v>
@@ -1312,13 +1312,13 @@
         <v>6.2436</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.568</v>
+        <v>-1.7879</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5353</v>
+        <v>-1.1484</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.0328</v>
+        <v>-0.6393</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3527</v>
@@ -1345,13 +1345,13 @@
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>-22.571</v>
+        <v>-20.1746</v>
       </c>
       <c r="E12" t="n">
-        <v>-13.9219</v>
+        <v>-12.608</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.648999999999999</v>
+        <v>-7.5666</v>
       </c>
       <c r="G12" t="n">
         <v>-14.5332</v>
@@ -1390,13 +1390,13 @@
         <v>8.5328</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.3501</v>
+        <v>0.04620000000000013</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5822000000000001</v>
+        <v>0.7316999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.7679</v>
+        <v>-0.6855</v>
       </c>
       <c r="V12" t="n">
         <v>-0.4848000000000002</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. SANTA BARBARA CARCELEN</t>
+          <t>I. CASAS GARRIDO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>-25.9463</v>
+        <v>-20.9717</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.455400000000001</v>
+        <v>-25.6076</v>
       </c>
       <c r="F13" t="n">
-        <v>-24.4906</v>
+        <v>4.635900000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-24.5048</v>
+        <v>-10.8945</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.5985</v>
+        <v>-23.1533</v>
       </c>
       <c r="I13" t="n">
-        <v>-21.9061</v>
+        <v>12.2585</v>
       </c>
       <c r="J13" t="n">
-        <v>9.226799999999999</v>
+        <v>12.1867</v>
       </c>
       <c r="K13" t="n">
-        <v>12.8498</v>
+        <v>-5.5745</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.6228</v>
+        <v>17.7611</v>
       </c>
       <c r="M13" t="n">
-        <v>-33.7315</v>
+        <v>-23.0812</v>
       </c>
       <c r="N13" t="n">
-        <v>-15.4483</v>
+        <v>-17.5787</v>
       </c>
       <c r="O13" t="n">
-        <v>-18.2834</v>
+        <v>-5.5025</v>
       </c>
       <c r="P13" t="n">
-        <v>12.0706</v>
+        <v>-13.1113</v>
       </c>
       <c r="Q13" t="n">
-        <v>-29.3448</v>
+        <v>-50.3647</v>
       </c>
       <c r="R13" t="n">
-        <v>41.4154</v>
+        <v>37.2532</v>
       </c>
       <c r="S13" t="n">
-        <v>7.892</v>
+        <v>-2.0428</v>
       </c>
       <c r="T13" t="n">
-        <v>5.6423</v>
+        <v>-0.6086</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2497</v>
+        <v>-1.4342</v>
       </c>
       <c r="V13" t="n">
-        <v>-21.4047</v>
+        <v>5.0771</v>
       </c>
       <c r="W13" t="n">
-        <v>13.0198</v>
+        <v>13.179</v>
       </c>
       <c r="X13" t="n">
-        <v>-34.4243</v>
+        <v>-8.101800000000001</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. CASAS GARRIDO</t>
+          <t>J. SANTA BARBARA CARCELEN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>26</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.9466</v>
+        <v>-28.151</v>
       </c>
       <c r="E14" t="n">
-        <v>-30.1457</v>
+        <v>-2.9552</v>
       </c>
       <c r="F14" t="n">
-        <v>2.1994</v>
+        <v>-25.1956</v>
       </c>
       <c r="G14" t="n">
-        <v>-10.8945</v>
+        <v>-24.5048</v>
       </c>
       <c r="H14" t="n">
-        <v>-23.1533</v>
+        <v>-2.5985</v>
       </c>
       <c r="I14" t="n">
-        <v>12.2585</v>
+        <v>-21.9061</v>
       </c>
       <c r="J14" t="n">
-        <v>12.1867</v>
+        <v>9.226799999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-5.5745</v>
+        <v>12.8498</v>
       </c>
       <c r="L14" t="n">
-        <v>17.7611</v>
+        <v>-3.6228</v>
       </c>
       <c r="M14" t="n">
-        <v>-23.0812</v>
+        <v>-33.7315</v>
       </c>
       <c r="N14" t="n">
-        <v>-17.5787</v>
+        <v>-15.4483</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.5025</v>
+        <v>-18.2834</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.1113</v>
+        <v>12.0706</v>
       </c>
       <c r="Q14" t="n">
-        <v>-50.3647</v>
+        <v>-29.3448</v>
       </c>
       <c r="R14" t="n">
-        <v>37.2532</v>
+        <v>41.4154</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.0174</v>
+        <v>5.6875</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.147</v>
+        <v>4.1426</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.8711</v>
+        <v>1.5452</v>
       </c>
       <c r="V14" t="n">
-        <v>5.0771</v>
+        <v>-21.4047</v>
       </c>
       <c r="W14" t="n">
-        <v>13.179</v>
+        <v>13.0198</v>
       </c>
       <c r="X14" t="n">
-        <v>-8.101800000000001</v>
+        <v>-34.4243</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. LOPES MARQUES</t>
+          <t>L. FAIAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-43.7654</v>
+        <v>-41.7506</v>
       </c>
       <c r="E15" t="n">
-        <v>-29.3562</v>
+        <v>-33.6582</v>
       </c>
       <c r="F15" t="n">
-        <v>-14.4089</v>
+        <v>-8.092899999999998</v>
       </c>
       <c r="G15" t="n">
-        <v>-19.2727</v>
+        <v>-39.1728</v>
       </c>
       <c r="H15" t="n">
-        <v>-4.2678</v>
+        <v>-13.9663</v>
       </c>
       <c r="I15" t="n">
-        <v>-15.005</v>
+        <v>-25.2066</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2635999999999998</v>
+        <v>-13.9081</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8584</v>
+        <v>2.2076</v>
       </c>
       <c r="L15" t="n">
-        <v>-3.122</v>
+        <v>-16.1159</v>
       </c>
       <c r="M15" t="n">
-        <v>-19.0087</v>
+        <v>-25.2649</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.1259</v>
+        <v>-16.1744</v>
       </c>
       <c r="O15" t="n">
-        <v>-11.8828</v>
+        <v>-9.0906</v>
       </c>
       <c r="P15" t="n">
-        <v>-19.7713</v>
+        <v>-4.9947</v>
       </c>
       <c r="Q15" t="n">
-        <v>-38.7103</v>
+        <v>-45.1619</v>
       </c>
       <c r="R15" t="n">
-        <v>18.9388</v>
+        <v>40.1669</v>
       </c>
       <c r="S15" t="n">
-        <v>7.6015</v>
+        <v>-0.4133999999999995</v>
       </c>
       <c r="T15" t="n">
-        <v>7.8663</v>
+        <v>1.654</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2647999999999999</v>
+        <v>-2.0676</v>
       </c>
       <c r="V15" t="n">
-        <v>-12.3227</v>
+        <v>2.8303</v>
       </c>
       <c r="W15" t="n">
-        <v>1.7512</v>
+        <v>23.7573</v>
       </c>
       <c r="X15" t="n">
-        <v>-14.0739</v>
+        <v>-20.9273</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. FAIAL</t>
+          <t>F. LOPEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D16" t="n">
-        <v>-49.6642</v>
+        <v>-46.8829</v>
       </c>
       <c r="E16" t="n">
-        <v>-39.9157</v>
+        <v>-31.3593</v>
       </c>
       <c r="F16" t="n">
-        <v>-9.748299999999999</v>
+        <v>-15.5236</v>
       </c>
       <c r="G16" t="n">
-        <v>-39.1728</v>
+        <v>-34.842</v>
       </c>
       <c r="H16" t="n">
-        <v>-13.9663</v>
+        <v>-14.1428</v>
       </c>
       <c r="I16" t="n">
-        <v>-25.2066</v>
+        <v>-20.6996</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.9081</v>
+        <v>-10.1752</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2076</v>
+        <v>-1.7544</v>
       </c>
       <c r="L16" t="n">
-        <v>-16.1159</v>
+        <v>-8.4209</v>
       </c>
       <c r="M16" t="n">
-        <v>-25.2649</v>
+        <v>-24.6671</v>
       </c>
       <c r="N16" t="n">
-        <v>-16.1744</v>
+        <v>-12.388</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.0906</v>
+        <v>-12.2788</v>
       </c>
       <c r="P16" t="n">
-        <v>-4.9947</v>
+        <v>-0.4161999999999998</v>
       </c>
       <c r="Q16" t="n">
-        <v>-45.1619</v>
+        <v>-22.685</v>
       </c>
       <c r="R16" t="n">
-        <v>40.1669</v>
+        <v>22.2686</v>
       </c>
       <c r="S16" t="n">
-        <v>-8.3268</v>
+        <v>-6.112299999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.6034</v>
+        <v>-4.1956</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.7235</v>
+        <v>-1.9169</v>
       </c>
       <c r="V16" t="n">
-        <v>2.8303</v>
+        <v>-5.5124</v>
       </c>
       <c r="W16" t="n">
-        <v>23.7573</v>
+        <v>5.6962</v>
       </c>
       <c r="X16" t="n">
-        <v>-20.9273</v>
+        <v>-11.2084</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. LOPEZ JIMENEZ</t>
+          <t>A. LOPES MARQUES</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-51.8295</v>
+        <v>-50.1391</v>
       </c>
       <c r="E17" t="n">
-        <v>-34.5604</v>
+        <v>-36.0511</v>
       </c>
       <c r="F17" t="n">
-        <v>-17.2694</v>
+        <v>-14.088</v>
       </c>
       <c r="G17" t="n">
-        <v>-34.842</v>
+        <v>-19.2727</v>
       </c>
       <c r="H17" t="n">
-        <v>-14.1428</v>
+        <v>-4.2678</v>
       </c>
       <c r="I17" t="n">
-        <v>-20.6996</v>
+        <v>-15.005</v>
       </c>
       <c r="J17" t="n">
-        <v>-10.1752</v>
+        <v>-0.2635999999999998</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.7544</v>
+        <v>2.8584</v>
       </c>
       <c r="L17" t="n">
-        <v>-8.4209</v>
+        <v>-3.122</v>
       </c>
       <c r="M17" t="n">
-        <v>-24.6671</v>
+        <v>-19.0087</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.388</v>
+        <v>-7.1259</v>
       </c>
       <c r="O17" t="n">
-        <v>-12.2788</v>
+        <v>-11.8828</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4161999999999998</v>
+        <v>-19.7713</v>
       </c>
       <c r="Q17" t="n">
-        <v>-22.685</v>
+        <v>-38.7103</v>
       </c>
       <c r="R17" t="n">
-        <v>22.2686</v>
+        <v>18.9388</v>
       </c>
       <c r="S17" t="n">
-        <v>-11.0592</v>
+        <v>1.2279</v>
       </c>
       <c r="T17" t="n">
-        <v>-7.3964</v>
+        <v>1.1716</v>
       </c>
       <c r="U17" t="n">
-        <v>-3.6626</v>
+        <v>0.05599999999999983</v>
       </c>
       <c r="V17" t="n">
-        <v>-5.5124</v>
+        <v>-12.3227</v>
       </c>
       <c r="W17" t="n">
-        <v>5.6962</v>
+        <v>1.7512</v>
       </c>
       <c r="X17" t="n">
-        <v>-11.2084</v>
+        <v>-14.0739</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-269.6525</v>
+        <v>-238.1542</v>
       </c>
       <c r="E18" t="n">
-        <v>-138.448</v>
+        <v>-124.0947</v>
       </c>
       <c r="F18" t="n">
-        <v>-131.203</v>
+        <v>-114.0587</v>
       </c>
       <c r="G18" t="n">
         <v>-170.4536</v>
@@ -1849,7 +1849,7 @@
         <v>-127.114</v>
       </c>
       <c r="P18" t="n">
-        <v>9.3645</v>
+        <v>9.364500000000005</v>
       </c>
       <c r="Q18" t="n">
         <v>-380.8581</v>
@@ -1858,13 +1858,13 @@
         <v>390.2215</v>
       </c>
       <c r="S18" t="n">
-        <v>-34.54960000000001</v>
+        <v>-3.052199999999998</v>
       </c>
       <c r="T18" t="n">
-        <v>-2.646400000000003</v>
+        <v>11.7072</v>
       </c>
       <c r="U18" t="n">
-        <v>-31.9037</v>
+        <v>-14.7592</v>
       </c>
       <c r="V18" t="n">
         <v>-74.0146</v>
